--- a/export.xlsx
+++ b/export.xlsx
@@ -1093,7 +1093,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16-11-2024</t>
+          <t>16-01-2025</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16-11-2024</t>
+          <t>16-01-2025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1739,7 +1739,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16-11-2024</t>
+          <t>16-01-2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2632,7 +2632,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16-11-2024</t>
+          <t>16-01-2025</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16-11-2024</t>
+          <t>16-01-2025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
